--- a/beamline_publication_data.xlsx
+++ b/beamline_publication_data.xlsx
@@ -507,17 +507,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Soft X-ray Scattering &amp; Spectroscopy</t>
+          <t>Electronic Structure Techniques</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G3" s="2">
         <f>E3/D3</f>
@@ -528,7 +528,7 @@
         <v/>
       </c>
       <c r="I3" t="n">
-        <v>378</v>
+        <v>899</v>
       </c>
       <c r="J3" s="2">
         <f>I3/D3</f>
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Imaging</t>
+          <t>Imaging and Microscopy</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="E4" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G4" s="2">
         <f>E4/D4</f>
@@ -569,7 +569,7 @@
         <v/>
       </c>
       <c r="I4" t="n">
-        <v>3675</v>
+        <v>6486</v>
       </c>
       <c r="J4" s="2">
         <f>I4/D4</f>
@@ -589,17 +589,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Imaging</t>
+          <t>BioImaging</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="E5" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G5" s="2">
         <f>E5/D5</f>
@@ -610,7 +610,7 @@
         <v/>
       </c>
       <c r="I5" t="n">
-        <v>895</v>
+        <v>1934</v>
       </c>
       <c r="J5" s="2">
         <f>I5/D5</f>
@@ -634,13 +634,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G6" s="2">
         <f>E6/D6</f>
@@ -651,7 +651,7 @@
         <v/>
       </c>
       <c r="I6" t="n">
-        <v>415</v>
+        <v>1204</v>
       </c>
       <c r="J6" s="2">
         <f>I6/D6</f>
@@ -671,17 +671,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Imaging</t>
+          <t>Imaging and Microscopy</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="E7" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G7" s="2">
         <f>E7/D7</f>
@@ -692,7 +692,7 @@
         <v/>
       </c>
       <c r="I7" t="n">
-        <v>2262</v>
+        <v>4128</v>
       </c>
       <c r="J7" s="2">
         <f>I7/D7</f>
@@ -712,17 +712,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hard X-ray Scattering &amp; Spectroscopy</t>
+          <t>Spectroscopy</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>145</v>
+        <v>219</v>
       </c>
       <c r="E8" t="n">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G8" s="2">
         <f>E8/D8</f>
@@ -733,7 +733,7 @@
         <v/>
       </c>
       <c r="I8" t="n">
-        <v>2019</v>
+        <v>3987</v>
       </c>
       <c r="J8" s="2">
         <f>I8/D8</f>
@@ -753,17 +753,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hard X-ray Scattering &amp; Spectroscopy</t>
+          <t>Spectroscopy</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>445</v>
+        <v>635</v>
       </c>
       <c r="E9" t="n">
-        <v>310</v>
+        <v>436</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G9" s="2">
         <f>E9/D9</f>
@@ -774,7 +774,7 @@
         <v/>
       </c>
       <c r="I9" t="n">
-        <v>14526</v>
+        <v>31852</v>
       </c>
       <c r="J9" s="2">
         <f>I9/D9</f>
@@ -794,17 +794,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Soft X-ray Scattering &amp; Spectroscopy</t>
+          <t>Spectroscopy</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="E10" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G10" s="2">
         <f>E10/D10</f>
@@ -815,7 +815,7 @@
         <v/>
       </c>
       <c r="I10" t="n">
-        <v>1904</v>
+        <v>3288</v>
       </c>
       <c r="J10" s="2">
         <f>I10/D10</f>
@@ -835,17 +835,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Soft X-ray Scattering &amp; Spectroscopy</t>
+          <t>Spectroscopy</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="E11" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G11" s="2">
         <f>E11/D11</f>
@@ -856,7 +856,7 @@
         <v/>
       </c>
       <c r="I11" t="n">
-        <v>344</v>
+        <v>818</v>
       </c>
       <c r="J11" s="2">
         <f>I11/D11</f>
@@ -876,17 +876,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Imaging</t>
+          <t>Spectroscopy</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="E12" t="n">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G12" s="2">
         <f>E12/D12</f>
@@ -897,7 +897,7 @@
         <v/>
       </c>
       <c r="I12" t="n">
-        <v>1768</v>
+        <v>4401</v>
       </c>
       <c r="J12" s="2">
         <f>I12/D12</f>
@@ -917,17 +917,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hard X-ray Scattering &amp; Spectroscopy</t>
+          <t>Spectroscopy</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>270</v>
+        <v>358</v>
       </c>
       <c r="E13" t="n">
-        <v>148</v>
+        <v>196</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G13" s="2">
         <f>E13/D13</f>
@@ -938,7 +938,7 @@
         <v/>
       </c>
       <c r="I13" t="n">
-        <v>13805</v>
+        <v>22368</v>
       </c>
       <c r="J13" s="2">
         <f>I13/D13</f>
@@ -962,13 +962,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E14" t="n">
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G14" s="2">
         <f>E14/D14</f>
@@ -979,7 +979,7 @@
         <v/>
       </c>
       <c r="I14" t="n">
-        <v>173</v>
+        <v>240</v>
       </c>
       <c r="J14" s="2">
         <f>I14/D14</f>
@@ -1003,13 +1003,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>463</v>
+        <v>623</v>
       </c>
       <c r="E15" t="n">
-        <v>224</v>
+        <v>321</v>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G15" s="2">
         <f>E15/D15</f>
@@ -1020,7 +1020,7 @@
         <v/>
       </c>
       <c r="I15" t="n">
-        <v>10663</v>
+        <v>20549</v>
       </c>
       <c r="J15" s="2">
         <f>I15/D15</f>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="E16" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G16" s="2">
         <f>E16/D16</f>
@@ -1061,7 +1061,7 @@
         <v/>
       </c>
       <c r="I16" t="n">
-        <v>671</v>
+        <v>1175</v>
       </c>
       <c r="J16" s="2">
         <f>I16/D16</f>
@@ -1085,13 +1085,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>171</v>
+        <v>234</v>
       </c>
       <c r="E17" t="n">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="F17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G17" s="2">
         <f>E17/D17</f>
@@ -1102,7 +1102,7 @@
         <v/>
       </c>
       <c r="I17" t="n">
-        <v>1618</v>
+        <v>4079</v>
       </c>
       <c r="J17" s="2">
         <f>I17/D17</f>
@@ -1126,13 +1126,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>166</v>
+        <v>252</v>
       </c>
       <c r="E18" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G18" s="2">
         <f>E18/D18</f>
@@ -1143,7 +1143,7 @@
         <v/>
       </c>
       <c r="I18" t="n">
-        <v>1953</v>
+        <v>3633</v>
       </c>
       <c r="J18" s="2">
         <f>I18/D18</f>
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G19" s="2">
         <f>E19/D19</f>
@@ -1184,7 +1184,7 @@
         <v/>
       </c>
       <c r="I19" t="n">
-        <v>315</v>
+        <v>603</v>
       </c>
       <c r="J19" s="2">
         <f>I19/D19</f>
@@ -1208,13 +1208,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>282</v>
+        <v>471</v>
       </c>
       <c r="E20" t="n">
-        <v>109</v>
+        <v>218</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G20" s="2">
         <f>E20/D20</f>
@@ -1225,7 +1225,7 @@
         <v/>
       </c>
       <c r="I20" t="n">
-        <v>4433</v>
+        <v>9554</v>
       </c>
       <c r="J20" s="2">
         <f>I20/D20</f>
@@ -1249,13 +1249,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>203</v>
+        <v>347</v>
       </c>
       <c r="E21" t="n">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G21" s="2">
         <f>E21/D21</f>
@@ -1266,7 +1266,7 @@
         <v/>
       </c>
       <c r="I21" t="n">
-        <v>3257</v>
+        <v>7092</v>
       </c>
       <c r="J21" s="2">
         <f>I21/D21</f>
@@ -1286,17 +1286,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Imaging</t>
+          <t>Imaging and Microscopy</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="E22" t="n">
-        <v>68</v>
+        <v>116</v>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G22" s="2">
         <f>E22/D22</f>
@@ -1307,7 +1307,7 @@
         <v/>
       </c>
       <c r="I22" t="n">
-        <v>3764</v>
+        <v>7541</v>
       </c>
       <c r="J22" s="2">
         <f>I22/D22</f>
@@ -1331,13 +1331,13 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G23" s="2">
         <f>E23/D23</f>
@@ -1348,7 +1348,7 @@
         <v/>
       </c>
       <c r="I23" t="n">
-        <v>190</v>
+        <v>537</v>
       </c>
       <c r="J23" s="2">
         <f>I23/D23</f>
@@ -1368,17 +1368,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Soft X-ray Scattering &amp; Spectroscopy</t>
+          <t>Electronic Structure Techniques</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>68</v>
+        <v>117</v>
       </c>
       <c r="E24" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="F24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G24" s="2">
         <f>E24/D24</f>
@@ -1389,7 +1389,7 @@
         <v/>
       </c>
       <c r="I24" t="n">
-        <v>1242</v>
+        <v>2703</v>
       </c>
       <c r="J24" s="2">
         <f>I24/D24</f>
@@ -1409,17 +1409,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Soft X-ray Scattering &amp; Spectroscopy</t>
+          <t>Electronic Structure Techniques</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="E25" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G25" s="2">
         <f>E25/D25</f>
@@ -1430,7 +1430,7 @@
         <v/>
       </c>
       <c r="I25" t="n">
-        <v>1153</v>
+        <v>1880</v>
       </c>
       <c r="J25" s="2">
         <f>I25/D25</f>
@@ -1450,17 +1450,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Soft X-ray Scattering &amp; Spectroscopy</t>
+          <t>Electronic Structure Techniques</t>
         </is>
       </c>
       <c r="D26" t="n">
+        <v>14</v>
+      </c>
+      <c r="E26" t="n">
         <v>7</v>
       </c>
-      <c r="E26" t="n">
-        <v>2</v>
-      </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G26" s="2">
         <f>E26/D26</f>
@@ -1471,7 +1471,7 @@
         <v/>
       </c>
       <c r="I26" t="n">
-        <v>32</v>
+        <v>178</v>
       </c>
       <c r="J26" s="2">
         <f>I26/D26</f>
@@ -1491,17 +1491,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Soft X-ray Scattering &amp; Spectroscopy</t>
+          <t>Electronic Structure Techniques</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="E27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G27" s="2">
         <f>E27/D27</f>
@@ -1512,7 +1512,7 @@
         <v/>
       </c>
       <c r="I27" t="n">
-        <v>611</v>
+        <v>954</v>
       </c>
       <c r="J27" s="2">
         <f>I27/D27</f>
@@ -1532,17 +1532,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Soft X-ray Scattering &amp; Spectroscopy</t>
+          <t>Spectroscopy</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="E28" t="n">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G28" s="2">
         <f>E28/D28</f>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="I28" t="n">
-        <v>4577</v>
+        <v>8319</v>
       </c>
       <c r="J28" s="2">
         <f>I28/D28</f>
@@ -1573,17 +1573,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hard X-ray Scattering &amp; Spectroscopy</t>
+          <t>Hard X-ray Methods</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G29" s="2">
         <f>E29/D29</f>
@@ -1594,7 +1594,7 @@
         <v/>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="J29" s="2">
         <f>I29/D29</f>
@@ -1614,17 +1614,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hard X-ray Scattering &amp; Spectroscopy</t>
+          <t>Hard X-ray Methods</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>166</v>
+        <v>309</v>
       </c>
       <c r="E30" t="n">
-        <v>73</v>
+        <v>153</v>
       </c>
       <c r="F30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G30" s="2">
         <f>E30/D30</f>
@@ -1635,7 +1635,7 @@
         <v/>
       </c>
       <c r="I30" t="n">
-        <v>2950</v>
+        <v>6395</v>
       </c>
       <c r="J30" s="2">
         <f>I30/D30</f>
@@ -1655,17 +1655,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hard X-ray Scattering &amp; Spectroscopy</t>
+          <t>Hard X-ray Methods</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>356</v>
+        <v>449</v>
       </c>
       <c r="E31" t="n">
-        <v>159</v>
+        <v>222</v>
       </c>
       <c r="F31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G31" s="2">
         <f>E31/D31</f>
@@ -1676,7 +1676,7 @@
         <v/>
       </c>
       <c r="I31" t="n">
-        <v>11743</v>
+        <v>21210</v>
       </c>
       <c r="J31" s="2">
         <f>I31/D31</f>
